--- a/data/Pob_Col_Ant_Amva_Med.xlsx
+++ b/data/Pob_Col_Ant_Amva_Med.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D16A33-363F-4021-9C14-B51017BD7324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEE9CBA-8E8B-40DB-ACAB-9026A725986A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84B901FC-BEBE-42A9-A2BC-5B90DFC192D7}"/>
   </bookViews>
@@ -905,6 +905,9 @@
       <c r="A2">
         <v>1912</v>
       </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
       <c r="E2" s="1">
         <v>5472604</v>
       </c>
@@ -922,6 +925,9 @@
       <c r="A3">
         <v>1918</v>
       </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
       <c r="E3" s="1">
         <v>5855077</v>
       </c>
@@ -939,6 +945,9 @@
       <c r="A4">
         <v>1928</v>
       </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
       <c r="E4" s="1">
         <v>7851110</v>
       </c>
@@ -956,6 +965,9 @@
       <c r="A5">
         <v>1938</v>
       </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
       <c r="E5" s="1">
         <v>8697041</v>
       </c>
@@ -1372,6 +1384,10 @@
       <c r="D21" s="1">
         <v>52007050</v>
       </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22">
@@ -1386,6 +1402,10 @@
       <c r="D22" s="1">
         <v>53416767</v>
       </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23">
@@ -1400,6 +1420,10 @@
       <c r="D23" s="1">
         <v>54549153</v>
       </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24">
@@ -1414,6 +1438,10 @@
       <c r="D24" s="1">
         <v>55336024</v>
       </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25">
@@ -1428,6 +1456,10 @@
       <c r="D25" s="1">
         <v>55797218</v>
       </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26">
@@ -1442,6 +1474,10 @@
       <c r="D26" s="1">
         <v>55957823</v>
       </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27">
@@ -1456,6 +1492,10 @@
       <c r="D27" s="1">
         <v>55819537</v>
       </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28">
@@ -1470,6 +1510,10 @@
       <c r="D28" s="1">
         <v>55407876</v>
       </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29">
@@ -1484,6 +1528,10 @@
       <c r="D29" s="1">
         <v>54729955</v>
       </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30">
@@ -1498,6 +1546,10 @@
       <c r="D30" s="1">
         <v>53812957</v>
       </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31">
@@ -1512,6 +1564,10 @@
       <c r="D31" s="1">
         <v>52675458</v>
       </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
